--- a/Result/profitability/2329.xlsx
+++ b/Result/profitability/2329.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.11</v>
       </c>
       <c r="M2" t="n">
-        <v>0.39875</v>
+        <v>0.445</v>
       </c>
       <c r="N2" t="n">
-        <v>13.4575</v>
+        <v>13.515</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.46</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3100000000000001</v>
+        <v>0.355</v>
       </c>
       <c r="N3" t="n">
-        <v>12.88875</v>
+        <v>12.84125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.05</v>
       </c>
       <c r="M4" t="n">
-        <v>0.28375</v>
+        <v>0.3275</v>
       </c>
       <c r="N4" t="n">
-        <v>12.67</v>
+        <v>12.675</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.62</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3275</v>
+        <v>0.3375</v>
       </c>
       <c r="N5" t="n">
-        <v>12.2425</v>
+        <v>12.0275</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.23</v>
       </c>
       <c r="M6" t="n">
-        <v>0.23125</v>
+        <v>0.23375</v>
       </c>
       <c r="N6" t="n">
-        <v>10.48625</v>
+        <v>10.10375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.02499999999999999</v>
+        <v>-0.07875000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>8.720000000000001</v>
+        <v>8.4575</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1875</v>
+        <v>-0.15125</v>
       </c>
       <c r="N8" t="n">
-        <v>7.398750000000001</v>
+        <v>7.456250000000001</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
         <v>-0.1</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3125000000000001</v>
+        <v>-0.3125</v>
       </c>
       <c r="N13" t="n">
         <v>6.263750000000001</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2329</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5476</v>
+      </c>
+      <c r="D75" t="n">
+        <v>4751</v>
+      </c>
+      <c r="E75" t="n">
+        <v>726</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="G75" t="n">
+        <v>345</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>6.31%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>108</v>
+      </c>
+      <c r="J75" t="n">
+        <v>453</v>
+      </c>
+      <c r="K75" t="n">
+        <v>408</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N75" t="n">
+        <v>14.0375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8787878787878787</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.4600000000000009</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.03596559812353406</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.07999999999999996</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.720000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1148964595858384</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
